--- a/output/pdf_financials_xlsx/VCM.xlsx
+++ b/output/pdf_financials_xlsx/VCM.xlsx
@@ -6637,7 +6637,7 @@
         <v>1.077</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="N91" s="3" t="n">
         <v>2.098</v>
@@ -6687,43 +6687,43 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.761</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.803</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.808</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.228</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.662</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.965</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.041</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>8.208</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.838</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.407</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.141</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>3.111</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="S92" s="1" t="inlineStr">
         <is>
@@ -12822,7 +12822,11 @@
           <t>Reserves 5,966</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -16348,7 +16352,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -24348,7 +24356,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -28046,7 +28058,11 @@
           <t>Reserves 4,104</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VCM.xlsx
+++ b/output/pdf_financials_xlsx/VCM.xlsx
@@ -9382,19 +9382,19 @@
         <v>-1.816</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>-2.868</v>
+        <v>-2.727</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-1.075</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-2.377</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-5.868</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-3.012</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>-2.659</v>
@@ -9445,19 +9445,19 @@
         <v>19.224</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>8.574</v>
+        <v>8.715</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>9.833</v>
+        <v>8.757999999999999</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>20.047</v>
+        <v>17.67</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>3.333</v>
+        <v>-2.535</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-11.005</v>
+        <v>-14.017</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>0.054</v>
@@ -41660,7 +41660,11 @@
           <t>Capital expenditures, net 29</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>CapitalExpenditure</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -44084,7 +44088,11 @@
           <t>Capital expenditures, net 30</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>CapitalExpenditure</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -46496,7 +46504,11 @@
           <t>Capital expenditures, net 31</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>CapitalExpenditure</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -90876,7 +90888,7 @@
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">

--- a/output/pdf_financials_xlsx/VCM.xlsx
+++ b/output/pdf_financials_xlsx/VCM.xlsx
@@ -2212,16 +2212,16 @@
         <v>0.162</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>5.878</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>5.448</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>3.317</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0</v>
@@ -2275,16 +2275,16 @@
         <v>3.456</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.291</v>
+        <v>4.587</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>14.618</v>
+        <v>20.066</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>22.402</v>
+        <v>27.232</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>30.157</v>
+        <v>33.474</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>21.275</v>
@@ -2338,16 +2338,16 @@
         <v>3.052841722170203</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-1.527214224030852</v>
+        <v>5.426283226668875</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>15.26827586927231</v>
+        <v>20.95862796503065</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>24.55040603184693</v>
+        <v>29.84361472454492</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>33.24734027892619</v>
+        <v>36.90425004134281</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>23.3945458544095</v>
@@ -7168,22 +7168,22 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.162</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>5.878</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>5.448</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>3.317</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>0</v>
@@ -61844,7 +61844,11 @@
           <t>Depreciation of property, plant and equipment 10</t>
         </is>
       </c>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
           <t>-</t>
@@ -68510,7 +68514,7 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">

--- a/output/pdf_financials_xlsx/VCM.xlsx
+++ b/output/pdf_financials_xlsx/VCM.xlsx
@@ -1739,10 +1739,10 @@
         <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>10.257</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
+        <v>7.019</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>0</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>0</v>
+        <v>1.854</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0</v>
@@ -2958,59 +2958,53 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D40" s="3" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0.065</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>1.978</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.134</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>0.163</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>0.107</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.116</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>0.051</v>
       </c>
     </row>
     <row r="41">
@@ -3040,43 +3034,43 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>23.818</v>
+        <v>25.796</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>13.442</v>
+        <v>13.454</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>11.736</v>
+        <v>11.773</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>13.114</v>
+        <v>13.128</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>4.674</v>
+        <v>4.688</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>12.972</v>
+        <v>13.142</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>18.047</v>
+        <v>18.111</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15.154</v>
+        <v>15.288</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>24.908</v>
+        <v>24.93</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>28.784</v>
+        <v>28.813</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>49.655</v>
+        <v>49.818</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>57.662</v>
+        <v>57.769</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>70.139</v>
+        <v>70.255</v>
       </c>
       <c r="S41" s="1" t="inlineStr">
         <is>
@@ -3537,43 +3531,43 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>14.676</v>
+        <v>12.698</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>5.698</v>
+        <v>5.686</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.824</v>
+        <v>0.787</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.469</v>
+        <v>1.455</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>5.854</v>
+        <v>5.84</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.91</v>
+        <v>3.74</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>4.127</v>
+        <v>4.063</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.859</v>
+        <v>2.725</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.03</v>
+        <v>3.008</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>4.427</v>
+        <v>4.398</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>9.33</v>
+        <v>9.167</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>16.932</v>
+        <v>16.825</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>9.266999999999999</v>
+        <v>9.151</v>
       </c>
       <c r="S48" s="1" t="inlineStr">
         <is>
@@ -4399,15 +4393,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C60" s="3" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0.099</v>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
@@ -4901,59 +4891,53 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D67" s="3" t="n">
+        <v>7.622</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>5.929</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>5.551</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>5.357</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>5.268</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>4.961</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>7.467</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>6.907</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>10.473</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>16.01</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>26.774</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>27.902</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>21.239</v>
+      </c>
+      <c r="S67" s="3" t="n">
+        <v>12.303</v>
       </c>
     </row>
     <row r="68">
@@ -7138,10 +7122,10 @@
         <v>-3.459</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>2.502</v>
+        <v>1.806</v>
       </c>
       <c r="O99" s="3" t="n">
-        <v>-2.185</v>
+        <v>-0.331</v>
       </c>
       <c r="P99" s="3" t="n">
         <v>8.689</v>
@@ -8050,7 +8034,7 @@
         </is>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-0.898</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
@@ -8062,7 +8046,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-60.522</v>
       </c>
       <c r="H114" s="3" t="n">
         <v>0</v>
@@ -8119,13 +8103,13 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.791</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>35.823</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
@@ -8176,10 +8160,10 @@
         </is>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.045</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.27</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>0</v>
@@ -36614,7 +36598,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -37448,7 +37436,11 @@
           <t>Deferred income tax recovery 14</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -40944,7 +40936,11 @@
           <t>Deferred income tax expense (recovery) 14</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -43036,11 +43032,7 @@
           <t>Net income (loss) from continuing operations $</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+      <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -43564,7 +43556,11 @@
           <t>Deferred income tax expense (recovery) 15</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -45666,11 +45662,7 @@
           <t>Net (loss) income from continuing operations $</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+      <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -48190,7 +48182,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
@@ -49028,11 +49024,7 @@
           <t>Net (loss) income from continuing operations $</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+      <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
@@ -62356,7 +62348,11 @@
           <t>Deferred income tax expense 24</t>
         </is>
       </c>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr">
         <is>
           <t>-</t>
@@ -65684,7 +65680,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D539" t="inlineStr"/>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E539" t="inlineStr">
         <is>
           <t>-</t>
@@ -65790,7 +65790,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E540" t="inlineStr">
         <is>
           <t>-</t>
@@ -66626,7 +66630,11 @@
           <t>Deferred income tax expense 23</t>
         </is>
       </c>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr">
         <is>
           <t>-</t>
@@ -67462,7 +67470,11 @@
           <t>Proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D556" t="inlineStr"/>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E556" t="inlineStr">
         <is>
           <t>-</t>
@@ -69566,7 +69578,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D576" t="inlineStr"/>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E576" t="inlineStr">
         <is>
           <t>-</t>
@@ -69776,7 +69792,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D578" t="inlineStr"/>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E578" t="inlineStr">
         <is>
           <t>-</t>
@@ -75276,7 +75296,11 @@
           <t>Net income from discontinued operations 4</t>
         </is>
       </c>
-      <c r="D632" t="inlineStr"/>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E632" t="inlineStr">
         <is>
           <t>-</t>
